--- a/201025_Results_Cali/output/m2/21102025_mod2_by_travel_mode.xlsx
+++ b/201025_Results_Cali/output/m2/21102025_mod2_by_travel_mode.xlsx
@@ -4216,27 +4216,27 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Compras y trámites</t>
+          <t>Estudio</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>11 (15.3%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>4 (8.2%)</t>
+          <t>1 (2.0%)</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>13 (9.6%)</t>
+          <t>8 (5.9%)</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>17 (25.8%)</t>
+          <t>3 (4.5%)</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -4250,7 +4250,7 @@
         </is>
       </c>
       <c r="J78">
-        <v>0.0005999999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Cuidado y familia (centro educativo, niños/as o jóvenes)</t>
+          <t>Otro</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>1 (2.0%)</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -4286,7 +4286,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>1 (1.5%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -4296,11 +4296,11 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>2 (1.9%)</t>
         </is>
       </c>
       <c r="J79">
-        <v>0.0005999999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
@@ -4316,27 +4316,27 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Cuidado y familia (otro lugar, niños/as o jóvenes)</t>
+          <t>Recreación y actividades personales</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>1 (1.4%)</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>6 (12.2%)</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>1 (0.7%)</t>
+          <t>5 (3.7%)</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>3 (4.5%)</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -4346,11 +4346,11 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>2 (1.9%)</t>
         </is>
       </c>
       <c r="J80">
-        <v>0.0005999999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
@@ -4366,41 +4366,41 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Estudio</t>
+          <t>Salud</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>8 (11.1%)</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>1 (2.0%)</t>
+          <t>8 (16.3%)</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>8 (5.9%)</t>
+          <t>10 (7.4%)</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>3 (4.5%)</t>
+          <t>17 (25.8%)</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>1 (14.3%)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>10 (9.7%)</t>
+          <t>33 (32.0%)</t>
         </is>
       </c>
       <c r="J81">
-        <v>0.0005999999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
@@ -4416,41 +4416,41 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Trabajo</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>50 (69.4%)</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>1 (2.0%)</t>
+          <t>29 (59.2%)</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2 (1.5%)</t>
+          <t>92 (67.6%)</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>23 (34.8%)</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>6 (85.7%)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>2 (1.9%)</t>
+          <t>43 (41.7%)</t>
         </is>
       </c>
       <c r="J82">
-        <v>0.0005999999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -4466,41 +4466,41 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Recreación, salud y actividades personales</t>
+          <t>Trámites</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>9 (12.5%)</t>
+          <t>1 (1.4%)</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>14 (28.6%)</t>
+          <t>1 (2.0%)</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>15 (11.0%)</t>
+          <t>6 (4.4%)</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>20 (30.3%)</t>
+          <t>6 (9.1%)</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>1 (14.3%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>35 (34.0%)</t>
+          <t>3 (2.9%)</t>
         </is>
       </c>
       <c r="J83">
-        <v>0.0005999999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
@@ -4516,41 +4516,41 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Trabajo</t>
+          <t>Viajes de cuidado</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>50 (69.4%)</t>
+          <t>10 (13.9%)</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>29 (59.2%)</t>
+          <t>3 (6.1%)</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>92 (67.6%)</t>
+          <t>10 (7.4%)</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>23 (34.8%)</t>
+          <t>12 (18.2%)</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>6 (85.7%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>43 (41.7%)</t>
+          <t>7 (6.8%)</t>
         </is>
       </c>
       <c r="J84">
-        <v>0.0005999999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
@@ -4600,7 +4600,7 @@
         </is>
       </c>
       <c r="J85">
-        <v>0.0005999999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86">
